--- a/Config/Datas/map_homestead.xlsx
+++ b/Config/Datas/map_homestead.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="logic_area_homestead_req" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="homestead_building" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="homestead_building_upgrade" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -507,4 +509,723 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>logic_area_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>building_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>max_level</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>逻辑区域id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>建筑id</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>显示名</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>最大等级</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>图标</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>elder_hall</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>长老厅</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>merchant_stall</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>商摊</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>teleport_gate</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>传送门</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>village_01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>village_hall</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>村政厅</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>logic_area_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>building_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>unlock_conds</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>unlock_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),CommonCheckCond</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),TalentUnlockCost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>逻辑区域id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>建筑id</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>目标等级</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>升级名</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>解锁条件</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>elder_hall</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>初建</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>搭建基础议事厅</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>wood,20|stone,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>elder_hall</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>扩建</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>增加办事窗口</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>wood,40|stone,20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>elder_hall</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>完善</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>提升管理效率</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>wood,60|stone,30|gold,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>merchant_stall</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>开张</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>启用商摊</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>wood,15|gold,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>merchant_stall</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>扩容</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>扩大交易规模</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>wood,30|gold,120</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>teleport_gate</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>修复</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>恢复传送功能</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>stone,25|gold,80</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>teleport_gate</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>强化</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>提升传送稳定性</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>stone,50|gold,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>village_01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>village_hall</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>接管</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>接管村政厅</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>wood,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>village_01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>village_hall</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>整顿</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>整顿村务</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>wood,25|gold,60</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Config/Datas/map_homestead.xlsx
+++ b/Config/Datas/map_homestead.xlsx
@@ -690,7 +690,6 @@
       <c r="F5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -714,7 +713,6 @@
       <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -738,7 +736,6 @@
       <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -762,7 +759,6 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -775,7 +771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,6 +815,11 @@
           <t>unlock_costs</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>daily_outputs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -861,6 +862,11 @@
           <t>(list#sep=|),TalentUnlockCost</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),TalentUnlockCost</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -903,6 +909,11 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -945,6 +956,11 @@
           <t>消耗</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>每日产出(控制城镇后结算)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -970,10 +986,14 @@
           <t>搭建基础议事厅</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>wood,20|stone,10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>gold,10</t>
         </is>
       </c>
     </row>
@@ -1001,10 +1021,14 @@
           <t>增加办事窗口</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>wood,40|stone,20</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>gold,20|wood,5</t>
         </is>
       </c>
     </row>
@@ -1032,10 +1056,14 @@
           <t>提升管理效率</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>wood,60|stone,30|gold,100</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>gold,40|desire_shard,1</t>
         </is>
       </c>
     </row>
@@ -1063,10 +1091,14 @@
           <t>启用商摊</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>wood,15|gold,50</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>gold,15</t>
         </is>
       </c>
     </row>
@@ -1094,10 +1126,14 @@
           <t>扩大交易规模</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>wood,30|gold,120</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>gold,35|wood,10</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1161,6 @@
           <t>恢复传送功能</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>stone,25|gold,80</t>
@@ -1156,7 +1191,6 @@
           <t>提升传送稳定性</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>stone,50|gold,200</t>
@@ -1187,10 +1221,14 @@
           <t>接管村政厅</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>wood,10</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>wood,8|gold,5</t>
         </is>
       </c>
     </row>
@@ -1218,10 +1256,14 @@
           <t>整顿村务</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>wood,25|gold,60</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>wood,15|gold,15</t>
         </is>
       </c>
     </row>
